--- a/india/data/india_cement_data_all.xlsx
+++ b/india/data/india_cement_data_all.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roberan\CICERO senter for klimaforskning\CM - Documents\GCP\Cement\data\India\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A4692F-07EE-461F-BA21-2572B5175E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="17400" tabRatio="718" firstSheet="9" activeTab="12" xr2:uid="{078DD7A2-32AD-4090-9EEA-F2342D7BD6F7}"/>
   </bookViews>
